--- a/information_request_forms/004_treasury_record_export_request_form--information_request_forms.xlsx
+++ b/information_request_forms/004_treasury_record_export_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_ledger'}</t>
+          <t>general_ledger</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General Ledger'}</t>
+          <t>General Ledger</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'account_balance'}</t>
+          <t>account_balance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Account Balance'}</t>
+          <t>Account Balance</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'transaction_history'}</t>
+          <t>transaction_history</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Transaction History'}</t>
+          <t>Transaction History</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'last_7_days'}</t>
+          <t>last_7_days</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Last 7 days'}</t>
+          <t>Last 7 days</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'last_30_days'}</t>
+          <t>last_30_days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Last 30 days'}</t>
+          <t>Last 30 days</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'last_90_days'}</t>
+          <t>last_90_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Last 90 days'}</t>
+          <t>Last 90 days</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excel'}</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excel'}</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'csv'}</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'CSV'}</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'internal'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Internal'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'ChatJimmy'}</t>
+          <t>ChatJimmy</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'default'}</t>
+          <t>default</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Default'}</t>
+          <t>Default</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'audit'}</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Audit'}</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'audit'}</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Audit'}</t>
+          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'exported'}</t>
+          <t>exported</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Exported'}</t>
+          <t>Exported</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_exported'}</t>
+          <t>not_exported</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Exported'}</t>
+          <t>Not Exported</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
